--- a/data/trans_orig/P24C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91292</t>
+          <t>92237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119592</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>66782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>91986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166451</t>
+          <t>166571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203844</t>
+          <t>204345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70738</t>
+          <t>70657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98996</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55774</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79763</t>
+          <t>81189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133700</t>
+          <t>134014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171699</t>
+          <t>171461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23558</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184003</t>
+          <t>184337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225629</t>
+          <t>226127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104996</t>
+          <t>105612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>268149</t>
+          <t>267254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>319650</t>
+          <t>320010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141876</t>
+          <t>138820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181865</t>
+          <t>181267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91075</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122620</t>
+          <t>121209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>245221</t>
+          <t>241605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296184</t>
+          <t>293909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46583</t>
+          <t>44980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56645</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87461</t>
+          <t>85359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121004</t>
+          <t>120100</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158708</t>
+          <t>154351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84456</t>
+          <t>82750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115627</t>
+          <t>113640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210988</t>
+          <t>211672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>257751</t>
+          <t>260662</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118785</t>
+          <t>117802</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153763</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>78321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109591</t>
+          <t>108729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205713</t>
+          <t>207811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252671</t>
+          <t>254596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51885</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82196</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52242</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>80447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>111834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154561</t>
+          <t>154260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>79731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110731</t>
+          <t>111304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>46280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133758</t>
+          <t>133370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172663</t>
+          <t>175149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64644</t>
+          <t>64399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94995</t>
+          <t>93944</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115349</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153626</t>
+          <t>154003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>74918</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75529</t>
+          <t>76783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>112185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45992</t>
+          <t>46448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69840</t>
+          <t>71729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>23001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25819</t>
+          <t>26098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67946</t>
+          <t>68223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>54102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79653</t>
+          <t>79398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,62 +3503,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5113</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1652</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>563792</t>
+          <t>563606</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>639292</t>
+          <t>636307</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>317656</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>898567</t>
+          <t>900423</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>996624</t>
+          <t>995130</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>472035</t>
+          <t>474465</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>546227</t>
+          <t>545618</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>322346</t>
+          <t>319714</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>378871</t>
+          <t>375955</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>813423</t>
+          <t>810310</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>907251</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>243775</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>304309</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>396724</t>
+          <t>405834</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>475745</t>
+          <t>484202</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>34351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56881</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>38346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57952</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87446</t>
+          <t>87819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73350</t>
+          <t>74663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>94337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152802</t>
+          <t>152069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187970</t>
+          <t>187394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43339</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>47745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54031</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85424</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41200</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67702</t>
+          <t>66854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20395</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41069</t>
+          <t>41764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67273</t>
+          <t>66199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101275</t>
+          <t>100972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172139</t>
+          <t>170390</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209272</t>
+          <t>211175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121227</t>
+          <t>120312</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>153983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>302026</t>
+          <t>302081</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>350519</t>
+          <t>353556</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,73%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82272</t>
+          <t>83089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117622</t>
+          <t>119204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>65617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96743</t>
+          <t>95946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162670</t>
+          <t>159515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207674</t>
+          <t>206911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37523</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66802</t>
+          <t>65309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>43515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>65785</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99349</t>
+          <t>101924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154838</t>
+          <t>155315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194721</t>
+          <t>191388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133532</t>
+          <t>133555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265158</t>
+          <t>266346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>314335</t>
+          <t>315921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80926</t>
+          <t>83169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117652</t>
+          <t>115616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82987</t>
+          <t>83114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114956</t>
+          <t>115729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177228</t>
+          <t>176942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224470</t>
+          <t>223895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73552</t>
+          <t>72188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77570</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>113588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89664</t>
+          <t>87850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124880</t>
+          <t>123001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80455</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113722</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177634</t>
+          <t>179449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224971</t>
+          <t>226697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100758</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136582</t>
+          <t>136403</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88241</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>121975</t>
+          <t>122984</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>199154</t>
+          <t>199727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>246303</t>
+          <t>247756</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>41464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59554</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43880</t>
+          <t>44008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>68974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100573</t>
+          <t>98046</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>72141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98169</t>
+          <t>97842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35450</t>
+          <t>34597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96386</t>
+          <t>97706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>126158</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>209175</t>
+          <t>208335</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>265597</t>
+          <t>268875</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>338066</t>
+          <t>338507</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>410611</t>
+          <t>410605</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>585405</t>
+          <t>585344</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>663028</t>
+          <t>664426</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>446884</t>
+          <t>442571</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>508856</t>
+          <t>508273</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1047935</t>
+          <t>1047411</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147182</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>448098</t>
+          <t>447789</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>518478</t>
+          <t>524096</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>326717</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>389445</t>
+          <t>391436</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>797125</t>
+          <t>794606</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>897632</t>
+          <t>892970</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016 (tasa de respuesta: 97,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55121</t>
+          <t>56160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83652</t>
+          <t>83537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107571</t>
+          <t>107303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>37983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128087</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158040</t>
+          <t>160636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30685</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46162</t>
+          <t>47015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>32919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57712</t>
+          <t>58358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>43632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60097</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94402</t>
+          <t>94911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132247</t>
+          <t>132014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165067</t>
+          <t>164152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120800</t>
+          <t>120747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236106</t>
+          <t>231823</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>276674</t>
+          <t>274593</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78514</t>
+          <t>80553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>56395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82437</t>
+          <t>83017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115349</t>
+          <t>115475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154542</t>
+          <t>153182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57822</t>
+          <t>59445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89677</t>
+          <t>92035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123547</t>
+          <t>123709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157310</t>
+          <t>154906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>97389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126977</t>
+          <t>126097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230588</t>
+          <t>230673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273515</t>
+          <t>272823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68589</t>
+          <t>69747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99318</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54661</t>
+          <t>54378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>80366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174764</t>
+          <t>174993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88923</t>
+          <t>89054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96503</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>129861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>85785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117183</t>
+          <t>116699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190103</t>
+          <t>191755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235727</t>
+          <t>236047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94966</t>
+          <t>94189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128166</t>
+          <t>128255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>85639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117002</t>
+          <t>117800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190194</t>
+          <t>189892</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235003</t>
+          <t>235287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>35714</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>63508</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52723</t>
+          <t>52868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77815</t>
+          <t>76752</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109849</t>
+          <t>109083</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68057</t>
+          <t>68021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94724</t>
+          <t>94665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>68465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122469</t>
+          <t>123499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156447</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47345</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62029</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,62 +11269,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4579</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24993</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>152920</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>203002</t>
+          <t>202916</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>104927</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>268494</t>
+          <t>265747</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>338442</t>
+          <t>332982</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>533918</t>
+          <t>536944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>604550</t>
+          <t>607611</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>398215</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>456641</t>
+          <t>454198</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>950462</t>
+          <t>946894</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1044514</t>
+          <t>1038487</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>384577</t>
+          <t>382325</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>449395</t>
+          <t>450863</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>324188</t>
+          <t>322678</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>380648</t>
+          <t>380689</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>725189</t>
+          <t>728954</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>814550</t>
+          <t>816917</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92237</t>
+          <t>91355</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>119401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66782</t>
+          <t>67435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91986</t>
+          <t>91133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166571</t>
+          <t>166405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204345</t>
+          <t>204343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70657</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>98438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,49 +860,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>47,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>67935</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56946</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80732</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>47,8%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67935</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56412</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81189</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>154</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134014</t>
+          <t>134573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171461</t>
+          <t>172355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24953</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30241</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>26518</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184337</t>
+          <t>183939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>226801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>103858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>267254</t>
+          <t>271215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320010</t>
+          <t>319072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138820</t>
+          <t>138399</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181267</t>
+          <t>179609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>92257</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121209</t>
+          <t>123666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>241605</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>293909</t>
+          <t>291540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44980</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>48198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85359</t>
+          <t>84876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120100</t>
+          <t>120877</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154351</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82750</t>
+          <t>83980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113640</t>
+          <t>114918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>211672</t>
+          <t>211491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260662</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117802</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152983</t>
+          <t>154420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>78358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>108478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207811</t>
+          <t>206131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>256956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51553</t>
+          <t>52512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51941</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>82519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111834</t>
+          <t>108880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154260</t>
+          <t>153757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79731</t>
+          <t>81142</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111304</t>
+          <t>111768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>47221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133370</t>
+          <t>135014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175149</t>
+          <t>173998</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>63820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>94890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>66966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>115941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154003</t>
+          <t>154007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>47196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74918</t>
+          <t>75303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>42628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76783</t>
+          <t>77080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112185</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49954</t>
+          <t>50192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46448</t>
+          <t>46094</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71729</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68223</t>
+          <t>67912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54102</t>
+          <t>53644</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79398</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21839</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>18643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>563606</t>
+          <t>565477</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>636307</t>
+          <t>633093</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>318528</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>377136</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>900423</t>
+          <t>899861</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>995130</t>
+          <t>994652</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>474465</t>
+          <t>472753</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>545618</t>
+          <t>546653</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>319714</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>375955</t>
+          <t>374681</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>810310</t>
+          <t>810633</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>905506</t>
+          <t>906603</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>243775</t>
+          <t>244946</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>305297</t>
+          <t>302760</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>144247</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>405834</t>
+          <t>402578</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>484202</t>
+          <t>480266</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>33106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56108</t>
+          <t>55501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38346</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>58640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>87866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99077</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69564</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94337</t>
+          <t>95010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152069</t>
+          <t>150815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187394</t>
+          <t>186355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41813</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47745</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>54114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83973</t>
+          <t>82693</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66854</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66199</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100972</t>
+          <t>101571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170390</t>
+          <t>171647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211175</t>
+          <t>206199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120312</t>
+          <t>119132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153983</t>
+          <t>152233</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>302081</t>
+          <t>301774</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>353556</t>
+          <t>350812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83089</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119204</t>
+          <t>118193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>66936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95946</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159515</t>
+          <t>160376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206911</t>
+          <t>205041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65309</t>
+          <t>66281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65785</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101924</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155315</t>
+          <t>153948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191388</t>
+          <t>192309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100568</t>
+          <t>101407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>131597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266346</t>
+          <t>265712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315921</t>
+          <t>316588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83169</t>
+          <t>83389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115616</t>
+          <t>117728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83114</t>
+          <t>85432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115729</t>
+          <t>115284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>175917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223895</t>
+          <t>224852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43306</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>72074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51245</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77550</t>
+          <t>76485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113588</t>
+          <t>116220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87850</t>
+          <t>87656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123001</t>
+          <t>122506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79272</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179449</t>
+          <t>177499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226697</t>
+          <t>224192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100380</t>
+          <t>99606</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136403</t>
+          <t>136012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>91002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>122984</t>
+          <t>121538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>199727</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247756</t>
+          <t>249248</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41464</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59556</t>
+          <t>61557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>66337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98046</t>
+          <t>97101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72141</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>97270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97706</t>
+          <t>95614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126158</t>
+          <t>128121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>23184</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21352</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29490</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,1%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>208335</t>
+          <t>207140</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117199</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>162056</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>338507</t>
+          <t>338756</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>410605</t>
+          <t>412082</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>585344</t>
+          <t>582646</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>664426</t>
+          <t>662657</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>442571</t>
+          <t>445468</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>508273</t>
+          <t>509000</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1047411</t>
+          <t>1048377</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1147182</t>
+          <t>1150002</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>447789</t>
+          <t>450037</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>524096</t>
+          <t>522206</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>326717</t>
+          <t>331626</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>391436</t>
+          <t>392608</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>794606</t>
+          <t>799820</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>892970</t>
+          <t>894166</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83537</t>
+          <t>84269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107303</t>
+          <t>108137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37983</t>
+          <t>36321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>57213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128686</t>
+          <t>127589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160636</t>
+          <t>159620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47015</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44835</t>
+          <t>44265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71889</t>
+          <t>73181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>57340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>43965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132014</t>
+          <t>132573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164152</t>
+          <t>165077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93830</t>
+          <t>92563</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120747</t>
+          <t>121993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231823</t>
+          <t>232848</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274593</t>
+          <t>275569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80553</t>
+          <t>78258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>56577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83017</t>
+          <t>83798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115475</t>
+          <t>114714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153182</t>
+          <t>155391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>49417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49488</t>
+          <t>49569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59445</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92035</t>
+          <t>92175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123709</t>
+          <t>123273</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154906</t>
+          <t>156505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97389</t>
+          <t>96965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126097</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230673</t>
+          <t>231121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272823</t>
+          <t>273652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69747</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>102089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54378</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80366</t>
+          <t>81246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132585</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174993</t>
+          <t>173122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65828</t>
+          <t>63608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55401</t>
+          <t>54661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89054</t>
+          <t>87526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>96992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129861</t>
+          <t>130938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>85785</t>
+          <t>84807</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116699</t>
+          <t>116141</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191755</t>
+          <t>191449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236047</t>
+          <t>238798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94189</t>
+          <t>95647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128255</t>
+          <t>128943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85639</t>
+          <t>86458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117800</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189892</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>235287</t>
+          <t>233945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35714</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63508</t>
+          <t>63217</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>31292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52868</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76752</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109083</t>
+          <t>109064</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68021</t>
+          <t>69160</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94665</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>46460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>68336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123499</t>
+          <t>123311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156846</t>
+          <t>158061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35887</t>
+          <t>35594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43847</t>
+          <t>42200</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>63023</t>
+          <t>61656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>151388</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>202916</t>
+          <t>204390</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>265747</t>
+          <t>267512</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>332982</t>
+          <t>332201</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>536944</t>
+          <t>532492</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>607611</t>
+          <t>605891</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>396063</t>
+          <t>391254</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>454198</t>
+          <t>454237</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>946894</t>
+          <t>950975</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1038487</t>
+          <t>1040076</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>382325</t>
+          <t>379365</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>450863</t>
+          <t>448964</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>322678</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>380689</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>728954</t>
+          <t>725046</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>816917</t>
+          <t>814744</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
